--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486405_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486405_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>A. BARCELLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4626</v>
+        <v>5.5217</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2431</v>
+        <v>4.9121</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7805</v>
+        <v>0.6097</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9688</v>
+        <v>0.3776</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5044</v>
+        <v>-1.0217</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.5356</v>
+        <v>1.3993</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9245</v>
+        <v>2.1843</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6567</v>
+        <v>-0.5713</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2677</v>
+        <v>2.7556</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9556</v>
+        <v>-1.8066</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1523</v>
+        <v>-0.4504</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.8033</v>
+        <v>-1.3563</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6101</v>
+        <v>2.1751</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.6101</v>
+        <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1163</v>
+        <v>-0.4209</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1887</v>
+        <v>-0.6621</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.305</v>
+        <v>0.2412</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>3.3899</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>3.3899</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BARCELLO</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0554</v>
+        <v>5.1619</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3533</v>
+        <v>5.5726</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7020999999999999</v>
+        <v>-0.4107</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3776</v>
+        <v>2.9688</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0217</v>
+        <v>4.5044</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3993</v>
+        <v>-1.5356</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1843</v>
+        <v>4.9245</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5713</v>
+        <v>4.6567</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7556</v>
+        <v>0.2677</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8066</v>
+        <v>-1.9556</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4504</v>
+        <v>-0.1523</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3563</v>
+        <v>-1.8033</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1751</v>
+        <v>2.6101</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1751</v>
+        <v>2.6101</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8872</v>
+        <v>-0.417</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2209</v>
+        <v>-0.4819</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3337</v>
+        <v>0.0649</v>
       </c>
       <c r="V3" t="n">
-        <v>3.3899</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.3899</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5314</v>
+        <v>3.1749</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4289</v>
+        <v>0.7642</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1025</v>
+        <v>2.4107</v>
       </c>
       <c r="G4" t="n">
         <v>0.8754999999999999</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.411</v>
+        <v>0.2325</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3869</v>
+        <v>-0.0517</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.024</v>
+        <v>0.2842</v>
       </c>
       <c r="V4" t="n">
         <v>0.5443</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0871</v>
+        <v>1.9877</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0185</v>
+        <v>0.8204</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1056</v>
+        <v>1.1672</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003</v>
+        <v>0.9053</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6298</v>
+        <v>0.4623</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6328</v>
+        <v>0.443</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5107</v>
+        <v>1.1461</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.8424</v>
+        <v>0.5141</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3531</v>
+        <v>0.6319</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5077</v>
+        <v>-0.2408</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2127</v>
+        <v>-0.0519</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7204</v>
+        <v>-0.1889</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>2.1751</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3239</v>
+        <v>0.0373</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8857</v>
+        <v>-0.3256</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4382</v>
+        <v>0.3629</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7602</v>
+        <v>-1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0835</v>
+        <v>1.3241</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2736</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8099</v>
+        <v>2.0131</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5147</v>
+        <v>0.003</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6544</v>
+        <v>-1.6298</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.1691</v>
+        <v>1.6328</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3589</v>
+        <v>0.5107</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1717</v>
+        <v>-1.8424</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8128</v>
+        <v>2.3531</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8736</v>
+        <v>-0.5077</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5173</v>
+        <v>0.2127</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3563</v>
+        <v>-0.7204</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6101</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6101</v>
+        <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9882</v>
+        <v>0.5609</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0853</v>
+        <v>0.2151</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0735</v>
+        <v>0.3458</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7757</v>
+        <v>1.1125</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4851</v>
+        <v>-0.1735</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2905</v>
+        <v>1.2859</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9053</v>
+        <v>-1.5147</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4623</v>
+        <v>1.6544</v>
       </c>
       <c r="I7" t="n">
-        <v>0.443</v>
+        <v>-3.1691</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1461</v>
+        <v>0.3589</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5141</v>
+        <v>2.1717</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6319</v>
+        <v>-1.8128</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2408</v>
+        <v>-1.8736</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0519</v>
+        <v>-0.5173</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1889</v>
+        <v>-1.3563</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1751</v>
+        <v>2.6101</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1751</v>
+        <v>2.6101</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1747</v>
+        <v>0.0171</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6609</v>
+        <v>-0.5323</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4862</v>
+        <v>0.5495</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1412</v>
+        <v>0.2488</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0634</v>
+        <v>-0.641</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2047</v>
+        <v>0.8898</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4123</v>
+        <v>-0.5386</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7206</v>
+        <v>-0.4684</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3084</v>
+        <v>-0.0701</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5875</v>
+        <v>0.0512</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7022</v>
+        <v>-0.5991</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1147</v>
+        <v>0.6502</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1752</v>
+        <v>-0.5898</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0184</v>
+        <v>0.1306</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1936</v>
+        <v>-0.7204</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0755</v>
+        <v>-0.3001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2211</v>
+        <v>-0.6922</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8544</v>
+        <v>0.392</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1789</v>
+        <v>-0.2787</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-1.1752</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7973</v>
+        <v>0.8964</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5386</v>
+        <v>-0.4123</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4684</v>
+        <v>-0.7206</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0701</v>
+        <v>0.3084</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0512</v>
+        <v>-0.5875</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5991</v>
+        <v>-0.7022</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6502</v>
+        <v>0.1147</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5898</v>
+        <v>0.1752</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1306</v>
+        <v>-0.0184</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7204</v>
+        <v>0.1936</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7279</v>
+        <v>0.6555</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0274</v>
+        <v>0.1094</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2996</v>
+        <v>0.5462</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3449</v>
+        <v>-0.975</v>
       </c>
       <c r="E12" t="n">
         <v>-3.6042</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2593</v>
+        <v>2.6291</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4955</v>
@@ -1390,13 +1390,13 @@
         <v>2.8276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.435</v>
       </c>
       <c r="T12" t="n">
         <v>-0.7619</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.043</v>
+        <v>0.3268</v>
       </c>
       <c r="V12" t="n">
         <v>0.3904</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7841</v>
+        <v>-4.4488</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0727</v>
+        <v>-2.7374</v>
       </c>
       <c r="F13" t="n">
         <v>-1.7113</v>
@@ -1468,10 +1468,10 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2055</v>
+        <v>0.1298</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3184</v>
+        <v>0.0168</v>
       </c>
       <c r="U13" t="n">
         <v>0.113</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.343</v>
+        <v>13.3431</v>
       </c>
       <c r="E14" t="n">
-        <v>4.178899999999998</v>
+        <v>4.178999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>9.164099999999999</v>
+        <v>9.1639</v>
       </c>
       <c r="G14" t="n">
         <v>-1.3305</v>
@@ -1531,7 +1531,7 @@
         <v>-8.902200000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8535999999999999</v>
+        <v>-0.8536000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>-8.0486</v>
@@ -1546,13 +1546,13 @@
         <v>19.5756</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06009999999999985</v>
+        <v>0.06010000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.1662</v>
+        <v>-3.1664</v>
       </c>
       <c r="U14" t="n">
-        <v>3.226599999999999</v>
+        <v>3.2265</v>
       </c>
       <c r="V14" t="n">
         <v>2.6503</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4493</v>
+        <v>2.7127</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8404</v>
+        <v>3.1757</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3911</v>
+        <v>-0.463</v>
       </c>
       <c r="G15" t="n">
         <v>2.3792</v>
@@ -1624,13 +1624,13 @@
         <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3872</v>
+        <v>-0.1238</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9589</v>
+        <v>-0.6237</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5718</v>
+        <v>0.4999</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1952</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1748</v>
+        <v>1.6288</v>
       </c>
       <c r="E16" t="n">
-        <v>1.559</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6158</v>
+        <v>0.8522</v>
       </c>
       <c r="G16" t="n">
         <v>0.5601</v>
@@ -1702,13 +1702,13 @@
         <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1149</v>
+        <v>0.569</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2161</v>
+        <v>0.4338</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1012</v>
+        <v>0.1352</v>
       </c>
       <c r="V16" t="n">
         <v>0.9347</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9819</v>
+        <v>1.5579</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2556</v>
+        <v>1.5851</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2738</v>
+        <v>-0.0272</v>
       </c>
       <c r="G17" t="n">
         <v>2.1283</v>
@@ -1780,13 +1780,13 @@
         <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>1.026</v>
+        <v>0.6021</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6237</v>
+        <v>-0.0469</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4023</v>
+        <v>0.6489</v>
       </c>
       <c r="V17" t="n">
         <v>-2.2599</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7689</v>
+        <v>1.4146</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1079</v>
+        <v>-0.6609</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8769</v>
+        <v>2.0755</v>
       </c>
       <c r="G18" t="n">
         <v>4.0264</v>
@@ -1858,13 +1858,13 @@
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2226</v>
+        <v>0.8682</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7294</v>
+        <v>-0.2824</v>
       </c>
       <c r="U18" t="n">
-        <v>1.952</v>
+        <v>1.1506</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6202</v>
+        <v>-0.5085</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0747</v>
+        <v>0.1865</v>
       </c>
       <c r="F19" t="n">
         <v>-0.695</v>
@@ -1936,10 +1936,10 @@
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.1118</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.1118</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0821</v>
+        <v>-1.2595</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2662</v>
+        <v>-0.9368</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8159</v>
+        <v>-0.3227</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0872</v>
@@ -2014,13 +2014,13 @@
         <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7674</v>
+        <v>0.59</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5432</v>
+        <v>-0.1274</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2242</v>
+        <v>0.7174</v>
       </c>
       <c r="V20" t="n">
         <v>0.1952</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9984</v>
+        <v>-1.4768</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9283</v>
+        <v>-0.7048</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.07</v>
+        <v>-0.772</v>
       </c>
       <c r="G21" t="n">
         <v>-0.006</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0996</v>
+        <v>-0.578</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5179</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3581</v>
+        <v>-0.0601</v>
       </c>
       <c r="V21" t="n">
         <v>1.4997</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2792</v>
+        <v>-1.5842</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.977</v>
+        <v>-0.6417</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3022</v>
+        <v>-0.9425</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7704</v>
@@ -2170,13 +2170,13 @@
         <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.139</v>
+        <v>-0.444</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.822</v>
+        <v>-0.4867</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.317</v>
+        <v>0.0427</v>
       </c>
       <c r="V22" t="n">
         <v>0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4952</v>
+        <v>-3.183</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0974</v>
+        <v>-1.5386</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3978</v>
+        <v>-1.6444</v>
       </c>
       <c r="G23" t="n">
         <v>-0.279</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.281</v>
+        <v>0.0312</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2774</v>
+        <v>-0.7186</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9964</v>
+        <v>0.7498</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7602</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0549</v>
+        <v>-4.256</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.026</v>
+        <v>-3.8025</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0289</v>
+        <v>-0.4534</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2753</v>
@@ -2326,13 +2326,13 @@
         <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.0231</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4111</v>
+        <v>0.1643</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.1879</v>
+        <v>-6.899</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.4909</v>
+        <v>-6.6027</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.697</v>
+        <v>-0.2963</v>
       </c>
       <c r="G25" t="n">
         <v>-5.4206</v>
@@ -2404,13 +2404,13 @@
         <v>0.87</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4623</v>
+        <v>-0.1733</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6693</v>
+        <v>-0.7811</v>
       </c>
       <c r="U25" t="n">
-        <v>0.207</v>
+        <v>0.6077</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.343</v>
+        <v>-11.853</v>
       </c>
       <c r="E26" t="n">
         <v>-9.164</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.179</v>
+        <v>-2.688800000000001</v>
       </c>
       <c r="G26" t="n">
         <v>1.330200000000001</v>
@@ -2482,13 +2482,13 @@
         <v>7.612500000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.06030000000000052</v>
+        <v>1.4301</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.2264</v>
+        <v>-3.2266</v>
       </c>
       <c r="U26" t="n">
-        <v>3.1663</v>
+        <v>4.656400000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-2.6505</v>
